--- a/Final QA signup and Login Page.xlsx
+++ b/Final QA signup and Login Page.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rethi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A300FA-66EF-4B05-AC44-597974FFE764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6672381-75A7-4B31-8F89-4BDBB6E58DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="219">
   <si>
     <t>Sign Up (TC_SUP_001 to TC_SUP_016)</t>
   </si>
@@ -445,9 +445,6 @@
     <t>TC018</t>
   </si>
   <si>
-    <t>Login</t>
-  </si>
-  <si>
     <t>Verify login fails with an incorrect password</t>
   </si>
   <si>
@@ -623,9 +620,6 @@
     <t>Verify Forgot Password page as Edit icon to change the email id</t>
   </si>
   <si>
-    <t>1. Check if the login page has edit icon above the email field                                                           2. Click the icon if available                                   3. Observe it</t>
-  </si>
-  <si>
     <t>Edit icon should be there and able to edit</t>
   </si>
   <si>
@@ -729,6 +723,9 @@
   </si>
   <si>
     <t>Module: Signin,  Signup &amp; Forgot Password |  Tester: Rethina Prakash |  Application: Tichi</t>
+  </si>
+  <si>
+    <t>1. Check if the login page has edit icon above the email field                                                               2. Click the icon if available                                   3. Observe it</t>
   </si>
 </sst>
 </file>
@@ -1013,11 +1010,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1054,14 +1048,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1085,13 +1072,20 @@
     <xf numFmtId="14" fontId="12" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1510,1318 +1504,1318 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+    </row>
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-    </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="F34" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="6" t="s">
+      <c r="J35" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="7" t="s">
+    <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="6" t="s">
+      <c r="J36" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="K36" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="J22" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G36" s="6" t="s">
+    <row r="37" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="31" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="41" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="str">
+      <c r="B41" s="28" t="str">
         <f>CONCATENATE("Total: ",G48," | Pass: ",G49," | Fail: ",G50," | Not Executed: ",G51)</f>
         <v xml:space="preserve">Total:  | Pass:  | Fail:  | Not Executed: </v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
     </row>
     <row r="42" spans="1:11" ht="69" x14ac:dyDescent="0.3">
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="3" t="str">
+      <c r="B43" s="2" t="str">
         <f>COUNTIF('Test Cases'!$J$6:$J$36,"Sign Up")&amp;" cases"</f>
         <v>16 cases</v>
       </c>
-      <c r="C43" s="3" t="str">
+      <c r="C43" s="2" t="str">
         <f>COUNTIF('Test Cases'!$J$6:$J$36,"Sign In Initial Page")&amp;" cases"</f>
         <v>5 cases</v>
       </c>
-      <c r="D43" s="3" t="str">
+      <c r="D43" s="2" t="str">
         <f>COUNTIF('Test Cases'!$J$6:$J$36,"Sign In Password Page")&amp;" cases"</f>
         <v>5 cases</v>
       </c>
-      <c r="E43" s="3" t="str">
+      <c r="E43" s="2" t="str">
         <f>COUNTIF('Test Cases'!$J$6:$J$36,"Forgot Password")&amp;" cases"</f>
         <v>4 cases</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="3" t="str">
+      <c r="B44" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"Positive")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"Positive")=1,"","s")</f>
         <v>1 case</v>
       </c>
-      <c r="C44" s="3" t="str">
+      <c r="C44" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"Positive")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"Positive")=1,"","s")</f>
         <v>1 case</v>
       </c>
-      <c r="D44" s="3" t="str">
+      <c r="D44" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"Positive")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"Positive")=1,"","s")</f>
         <v>1 case</v>
       </c>
-      <c r="E44" s="3" t="str">
+      <c r="E44" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"Positive")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"Positive")=1,"","s")</f>
         <v>2 cases</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="3" t="str">
+      <c r="B45" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"Negative")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"Negative")=1,"","s")</f>
         <v>9 cases</v>
       </c>
-      <c r="C45" s="3" t="str">
+      <c r="C45" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"Negative")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"Negative")=1,"","s")</f>
         <v>3 cases</v>
       </c>
-      <c r="D45" s="3" t="str">
+      <c r="D45" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"Negative")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"Negative")=1,"","s")</f>
         <v>3 cases</v>
       </c>
-      <c r="E45" s="3" t="str">
+      <c r="E45" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"Negative")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"Negative")=1,"","s")</f>
         <v>0 cases</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="3" t="str">
+      <c r="B46" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"Edge")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"Edge")=1,"","s")</f>
         <v>5 cases</v>
       </c>
-      <c r="C46" s="3" t="str">
+      <c r="C46" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"Edge")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"Edge")=1,"","s")</f>
         <v>0 cases</v>
       </c>
-      <c r="D46" s="3" t="str">
+      <c r="D46" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"Edge")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"Edge")=1,"","s")</f>
         <v>0 cases</v>
       </c>
-      <c r="E46" s="3" t="str">
+      <c r="E46" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"Edge")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"Edge")=1,"","s")</f>
         <v>0 cases</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="3" t="str">
+      <c r="B47" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"UI")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$K$6:$K$36,"UI")=1,"","s")</f>
         <v>1 case</v>
       </c>
-      <c r="C47" s="3" t="str">
+      <c r="C47" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"UI")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$K$6:$K$36,"UI")=1,"","s")</f>
         <v>1 case</v>
       </c>
-      <c r="D47" s="3" t="str">
+      <c r="D47" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"UI")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$K$6:$K$36,"UI")=1,"","s")</f>
         <v>1 case</v>
       </c>
-      <c r="E47" s="3" t="str">
+      <c r="E47" s="2" t="str">
         <f>COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"UI")&amp;" case"&amp;IF(COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$K$6:$K$36,"UI")=1,"","s")</f>
         <v>2 cases</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B48" s="3" t="str">
+      <c r="B48" s="2" t="str">
         <f>"Pass: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$I$6:$I$36,"Pass")&amp;"  Fail: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Sign Up",'Test Cases'!$I$6:$I$36,"Fail")</f>
         <v>Pass: 12  Fail: 4</v>
       </c>
-      <c r="C48" s="3" t="str">
+      <c r="C48" s="2" t="str">
         <f>"Pass: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$I$6:$I$36,"Pass")&amp;"  Fail: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Initial Page",'Test Cases'!$I$6:$I$36,"Fail")</f>
         <v>Pass: 4  Fail: 1</v>
       </c>
-      <c r="D48" s="3" t="str">
+      <c r="D48" s="2" t="str">
         <f>"Pass: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$I$6:$I$36,"Pass")&amp;"  Fail: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Sign In Password Page",'Test Cases'!$I$6:$I$36,"Fail")</f>
         <v>Pass: 4  Fail: 1</v>
       </c>
-      <c r="E48" s="3" t="str">
+      <c r="E48" s="2" t="str">
         <f>"Pass: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$I$6:$I$36,"Pass")&amp;"  Fail: "&amp;COUNTIFS('Test Cases'!$J$6:$J$36,"Forgot Password",'Test Cases'!$I$6:$I$36,"Fail")</f>
         <v>Pass: 3  Fail: 1</v>
       </c>
@@ -2845,176 +2839,176 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="30"/>
+    </row>
+    <row r="2" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="2" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B3" s="15" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B4" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="B5" s="22">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="19" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="26">
-        <v>46206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="19" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="B16" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
+      <c r="A17" s="20"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
+      <c r="A18" s="20"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
+      <c r="A19" s="20"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
+      <c r="A20" s="20"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
+      <c r="A21" s="20"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="24"/>
+      <c r="A22" s="20"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="24"/>
+      <c r="A23" s="20"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="24"/>
+      <c r="A24" s="20"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
+      <c r="A25" s="20"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="24"/>
+      <c r="A26" s="20"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
+      <c r="A27" s="20"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="24"/>
+      <c r="A28" s="20"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
+      <c r="A29" s="20"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
+      <c r="A30" s="20"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="B31" s="25"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
